--- a/data/trans_orig/IP1014-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1014-Edad-trans_orig.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3611</t>
+          <t>4036</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>117434</t>
+          <t>118049</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>223940</t>
+          <t>223515</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3249</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4861</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>639</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5818</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>249956</t>
+          <t>249355</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>248895</t>
+          <t>248993</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>501143</t>
+          <t>501522</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>506319</t>
+          <t>506322</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4535</t>
+          <t>3392</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3407</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>136980</t>
+          <t>138123</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>265641</t>
+          <t>265656</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3210</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>202430</t>
+          <t>202861</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>396919</t>
+          <t>396936</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>8159</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8699</t>
+          <t>8156</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>678079</t>
+          <t>677995</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>715780</t>
+          <t>714541</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>721379</t>
+          <t>721349</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1395022</t>
+          <t>1395565</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1402338</t>
+          <t>1402370</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>4934</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4518</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>654</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7067</t>
+          <t>6678</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>229145</t>
+          <t>229542</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>262583</t>
+          <t>262062</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>494509</t>
+          <t>494898</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>500781</t>
+          <t>500922</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4166</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>154405</t>
+          <t>153809</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>308703</t>
+          <t>309294</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>564</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5496</t>
+          <t>4994</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>570</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5050</t>
+          <t>5595</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>172461</t>
+          <t>172963</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>177394</t>
+          <t>177393</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>344244</t>
+          <t>343699</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>348934</t>
+          <t>348724</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4927</t>
+          <t>6325</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9086</t>
+          <t>9254</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2762</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11357</t>
+          <t>11708</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>702001</t>
+          <t>700603</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>739056</t>
+          <t>738888</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>746133</t>
+          <t>746185</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1443713</t>
+          <t>1443362</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1452308</t>
+          <t>1451880</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -5009,7 +5009,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3568</t>
+          <t>3592</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>254493</t>
+          <t>254469</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>463811</t>
+          <t>463472</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4555</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>4483</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>184017</t>
+          <t>183944</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>373585</t>
+          <t>372988</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -6033,47 +6033,47 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5246</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
           <t>617</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5357</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>615</t>
-        </is>
-      </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>739487</t>
+          <t>739598</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>744227</t>
+          <t>744225</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1443872</t>
+          <t>1443342</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1448600</t>
+          <t>1448598</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/IP1014-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1014-Edad-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>705</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3331</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3939</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4036</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>120675</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>117880</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,42%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,12%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>120675</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>118049</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,42%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>223515</t>
+          <t>223612</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1374</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4825</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3850</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1374</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4763</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>5390</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>252382</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>248931</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,46%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,1%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>378</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>252563</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>249355</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>250205</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,75%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,48%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,82%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>252382</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>248993</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,12%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>758</t>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>501522</t>
+          <t>501571</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>506322</t>
+          <t>506320</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3397</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>679</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3392</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3403</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3407</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>140836</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>138118</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,52%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,6%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>140836</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>138123</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,52%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>265656</t>
+          <t>265660</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,92 +1751,92 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3237</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3188</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3210</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>205407</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>202812</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,69%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,43%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>205407</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>202861</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,69%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>396936</t>
+          <t>396931</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3399</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1347</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7549</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3026</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3590</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>3399</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1351</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>8159</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8156</t>
+          <t>8259</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>719301</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>715151</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>721353</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,53%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,81%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1017</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>680379</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>677995</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>677431</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,91%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,47%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>719301</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>714541</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>721349</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,53%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,87%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2098</t>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1395565</t>
+          <t>1395462</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1402370</t>
+          <t>1401802</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2782,47 +2782,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>146281</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3017,67 +3017,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>1447</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5189</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>1339</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4934</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6238</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,57%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1447</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5039</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>796</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6678</t>
+          <t>6992</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>265654</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>261912</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,46%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,06%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>335</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>233137</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>229542</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>228238</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,43%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,9%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,34%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>265654</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>262062</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,11%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>704</t>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>494898</t>
+          <t>494584</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>500922</t>
+          <t>500780</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>337</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,107 +3355,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1362</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4023</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>1362</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4762</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4752</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1362</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4111</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>157209</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>154548</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,14%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,46%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>157209</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>153809</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,14%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>309294</t>
+          <t>308653</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,92 +3698,92 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1883</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5060</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,84%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1883</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>564</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4994</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1883</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>577</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5595</t>
+          <t>5909</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -3811,72 +3811,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>176074</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>172897</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>177385</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,94%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,16%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,68%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>176074</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>172963</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>177393</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,94%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>343699</t>
+          <t>343385</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>348724</t>
+          <t>348717</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4691</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2035</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>9563</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1339</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>6325</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5560</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>4691</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>9254</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>2671</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11708</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -4154,74 +4154,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1059</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>743451</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>738579</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>746107</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,37%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,72%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>705589</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>700603</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>701368</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,81%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1059</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>743451</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>738888</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>746185</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,37%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,76%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,74%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2075</t>
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1443362</t>
+          <t>1444532</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1451880</t>
+          <t>1452399</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4729,47 +4729,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4959,107 +4959,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3618</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>715</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3592</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3992</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>715</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>5106</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>257346</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>254443</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,72%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,6%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>257346</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>254469</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>463472</t>
+          <t>464586</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5302,92 +5302,92 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4423</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>1280</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4628</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1280</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4483</t>
+          <t>4504</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>187292</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>184149</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,32%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,65%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>187292</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>183944</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>372988</t>
+          <t>372967</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5758,47 +5758,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>173301</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,84 +5988,84 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5701</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1995</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5246</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
           <t>617</t>
@@ -6073,7 +6073,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>742849</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>739143</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>744250</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,23%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>742849</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>739598</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>744225</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1443342</t>
+          <t>1443163</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
